--- a/src/main/resources/reports/apk_9.xlsx
+++ b/src/main/resources/reports/apk_9.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="205">
   <si>
     <t xml:space="preserve">Наименование показателя</t>
   </si>
@@ -218,19 +218,101 @@
     <t xml:space="preserve">${winter_wheat_area.harvestedArea}</t>
   </si>
   <si>
-    <t xml:space="preserve">${winter_wheat.yield}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${winter_wheat.totalSalary}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${winter_wheat.seedsUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${winter_wheat.fertilizersUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${winter_wheat.fuelUsed}</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${winter_wheat.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalGrossHarvest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${winter_wheat.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalCost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val=""/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">crop_material_costs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val=""/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.winter_wheat.seeds}</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">${crop_material_costs.winter_wheat.fertilizersUsed}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${crop_material_costs.winter_wheat.fuelUsed}</t>
   </si>
   <si>
     <t xml:space="preserve">пшеница яровая</t>
@@ -245,19 +327,211 @@
     <t xml:space="preserve">${spring_wheat_area.harvestedArea}</t>
   </si>
   <si>
-    <t xml:space="preserve">${spring_wheat.yield}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${spring_wheat.totalSalary}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${spring_wheat.seedsUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${spring_wheat.fertilizersUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${spring_wheat.fuelUsed}</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${spring_wheat.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalGrossHarvest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${spring_wheat.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalCost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">crop_material_costs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">spring_wheat.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">seeds</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">crop_material_costs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">spring_wheat.fertilizersUsed}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">crop_material_costs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">spring_wheat.fuelUsed}</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">кукуруза (на зерно)</t>
@@ -309,19 +583,211 @@
     <t xml:space="preserve">${spring_barley_area.harvestedArea}</t>
   </si>
   <si>
-    <t xml:space="preserve">${spring_barley.yield}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${spring_barley.totalSalary}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${spring_barley.seedsUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${spring_barley.fertilizersUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${spring_barley.fuelUsed}</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${spring_barley.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalGrossHarvest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${spring_barley.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalCost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">crop_material_costs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">spring_barley.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">seeds</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">crop_material_costs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">spring_barley.fertilizersUsed}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">crop_material_costs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">spring_barley.fuelUsed}</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">из него:
@@ -376,27 +842,6 @@
     <t xml:space="preserve">92310</t>
   </si>
   <si>
-    <t xml:space="preserve">${soy_area.sownArea}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${soy_area.harvestedArea}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${soy.yield}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${soy.totalSalary}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${soy.seedsUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${soy.fertilizersUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${soy.fuelUsed}</t>
-  </si>
-  <si>
     <t xml:space="preserve">рапс озимый</t>
   </si>
   <si>
@@ -421,19 +866,77 @@
     <t xml:space="preserve">${sunflower_area.harvestedArea}</t>
   </si>
   <si>
-    <t xml:space="preserve">${sunflower.yield}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${sunflower.totalSalary}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${sunflower.seedsUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${sunflower.fertilizersUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${sunflower.fuelUsed}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${sunflower.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalGrossHarvest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">${sunflower.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalCost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">}</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">${crop_material_costs.sunflower.seeds}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${crop_material_costs.sunflower.fertilizersUsed}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${crop_material_costs.sunflower.fuelUsed}</t>
   </si>
   <si>
     <t xml:space="preserve">из него 
@@ -467,9 +970,6 @@
   </si>
   <si>
     <t xml:space="preserve">92421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Х</t>
   </si>
   <si>
     <t xml:space="preserve">помидоры (томаты)</t>
@@ -809,7 +1309,7 @@
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="[=0]\-;General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -854,6 +1354,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC77DBB"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val=""/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6AAB73"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -996,7 +1535,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1061,8 +1600,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1113,20 +1664,32 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1242,7 +1805,7 @@
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFC77DBB"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -1251,7 +1814,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF6AAB73"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1493,10 +2056,10 @@
         <f aca="false">SUM(G8:J8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="18" t="s">
         <v>30</v>
       </c>
       <c r="I8" s="15" t="s">
@@ -1526,16 +2089,16 @@
         <f aca="false">SUM(G9:J9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="20" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1546,30 +2109,30 @@
       <c r="B10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
@@ -1578,14 +2141,14 @@
       <c r="B12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
@@ -1594,14 +2157,14 @@
       <c r="B13" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
@@ -1610,14 +2173,14 @@
       <c r="B14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
@@ -1626,14 +2189,14 @@
       <c r="B15" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
@@ -1655,34 +2218,34 @@
         <f aca="false">SUM(G16:J16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="20" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="22" t="s">
         <v>63</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
@@ -1691,14 +2254,14 @@
       <c r="B18" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
@@ -1707,30 +2270,30 @@
       <c r="B19" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="22" t="s">
         <v>69</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
@@ -1739,30 +2302,30 @@
       <c r="B21" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1797,17 +2360,17 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="23" width="55.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="23" width="9.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="23" width="15.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="23" width="17.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="23" width="19.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="23" width="15.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="23" width="17.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="23" width="12.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="23" width="15.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="23" width="14.4"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1013" min="11" style="23" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="55.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="9.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="15.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="26" width="17.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="26" width="19.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="26" width="15.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="26" width="17.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="26" width="12.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="26" width="15.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="26" width="14.4"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1013" min="11" style="26" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1014" style="0" width="9.14"/>
   </cols>
   <sheetData>
@@ -1822,7 +2385,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3"/>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="27" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1844,7 +2407,7 @@
       <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="24"/>
+      <c r="E2" s="27"/>
       <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1860,7 +2423,7 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="24"/>
+      <c r="E3" s="27"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -1876,7 +2439,7 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="24"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
@@ -1902,7 +2465,7 @@
       <c r="D5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F5" s="6" t="n">
@@ -1925,38 +2488,38 @@
       <c r="A6" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="27" t="e">
+      <c r="C6" s="30" t="e">
         <f aca="false">C10+C7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D6" s="27" t="e">
+      <c r="D6" s="30" t="e">
         <f aca="false">D10+D7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E6" s="27" t="e">
+      <c r="E6" s="30" t="e">
         <f aca="false">E10+E7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="30" t="n">
         <f aca="false">F10+F7</f>
         <v>0</v>
       </c>
-      <c r="G6" s="27" t="e">
+      <c r="G6" s="30" t="e">
         <f aca="false">G10+G7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H6" s="27" t="e">
+      <c r="H6" s="30" t="e">
         <f aca="false">H10+H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I6" s="27" t="e">
+      <c r="I6" s="30" t="e">
         <f aca="false">I10+I7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J6" s="27" t="e">
+      <c r="J6" s="30" t="e">
         <f aca="false">J10+J7</f>
         <v>#VALUE!</v>
       </c>
@@ -1965,463 +2528,434 @@
       <c r="A7" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <f aca="false">SUM(G7:J7)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>85</v>
-      </c>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
+        <v>79</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-    </row>
-    <row r="10" customFormat="false" ht="41.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+    </row>
+    <row r="10" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>94</v>
+        <v>83</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>87</v>
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">SUM(G10:J10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>98</v>
+      <c r="G10" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
+      <c r="A11" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+    </row>
+    <row r="14" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="s">
+      <c r="B16" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-    </row>
-    <row r="14" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="s">
+      <c r="B17" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
+      <c r="B18" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="B19" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B20" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B21" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="s">
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B22" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-    </row>
-    <row r="19" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B23" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B24" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B25" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B26" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B27" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="36" t="s">
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B28" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36" t="s">
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B29" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="s">
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B30" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="33" t="s">
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="B31" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37" t="s">
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+    </row>
+    <row r="32" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B32" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-    </row>
-    <row r="32" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2465,11 +2999,11 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -2485,7 +3019,7 @@
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
@@ -2504,7 +3038,7 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
@@ -2527,28 +3061,28 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="L4" s="40" t="s">
-        <v>155</v>
+        <v>146</v>
+      </c>
+      <c r="L4" s="46" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2565,569 +3099,569 @@
         <v>18</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="49" t="n">
+        <f aca="false">C13+C7+C25</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="49" t="n">
+        <f aca="false">D13+D7+D25</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="49" t="n">
+        <f aca="false">E13+E7+E25</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="49" t="n">
+        <f aca="false">F13+F7+F25</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="49" t="n">
+        <f aca="false">G13+G7+G25</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="49" t="n">
+        <f aca="false">H13+H7+H25</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="49" t="n">
+        <f aca="false">I13+I7+I25</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="49" t="n">
+        <f aca="false">J13+J7+J25</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="49" t="n">
+        <f aca="false">K13+K7+K25</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="49" t="n">
+        <f aca="false">L13+L7+L25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+    </row>
+    <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="s">
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B10" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="43" t="n">
-        <f aca="false">C13+C7+C25</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="43" t="n">
-        <f aca="false">D13+D7+D25</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="43" t="n">
-        <f aca="false">E13+E7+E25</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="43" t="n">
-        <f aca="false">F13+F7+F25</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="43" t="n">
-        <f aca="false">G13+G7+G25</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="43" t="n">
-        <f aca="false">H13+H7+H25</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="43" t="n">
-        <f aca="false">I13+I7+I25</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="43" t="n">
-        <f aca="false">J13+J7+J25</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="43" t="n">
-        <f aca="false">K13+K7+K25</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="43" t="n">
-        <f aca="false">L13+L7+L25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-    </row>
-    <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-    </row>
-    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
     </row>
     <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
+        <v>166</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+    </row>
+    <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="50" t="n">
+        <f aca="false">C17</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="50" t="n">
+        <f aca="false">D17</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="50" t="n">
+        <f aca="false">E17</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="50" t="n">
+        <f aca="false">F17</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="50" t="n">
+        <f aca="false">G17</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="50" t="n">
+        <f aca="false">H17</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="50" t="n">
+        <f aca="false">I17</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="50" t="n">
+        <f aca="false">J17</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="50" t="n">
+        <f aca="false">K17</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="50" t="n">
+        <f aca="false">L17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+    </row>
+    <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+    </row>
+    <row r="16" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B16" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-    </row>
-    <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="s">
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+    </row>
+    <row r="17" customFormat="false" ht="24.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B17" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="44" t="n">
-        <f aca="false">C17</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="44" t="n">
-        <f aca="false">D17</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="44" t="n">
-        <f aca="false">E17</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="44" t="n">
-        <f aca="false">F17</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="44" t="n">
-        <f aca="false">G17</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="44" t="n">
-        <f aca="false">H17</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="44" t="n">
-        <f aca="false">I17</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="44" t="n">
-        <f aca="false">J17</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="44" t="n">
-        <f aca="false">K17</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="44" t="n">
-        <f aca="false">L17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
+      <c r="C17" s="51" t="n">
+        <f aca="false">C18</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="51" t="n">
+        <f aca="false">D18</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="51" t="n">
+        <f aca="false">E18</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="51" t="n">
+        <f aca="false">F18</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="51" t="n">
+        <f aca="false">G18</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="51" t="n">
+        <f aca="false">H18</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="51" t="n">
+        <f aca="false">I18</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="51" t="n">
+        <f aca="false">J18</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="51" t="n">
+        <f aca="false">K18</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="51" t="n">
+        <f aca="false">L18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B18" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-    </row>
-    <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B19" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-    </row>
-    <row r="16" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B20" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-    </row>
-    <row r="17" customFormat="false" ht="24.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B21" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="C17" s="45" t="n">
-        <f aca="false">C18</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="45" t="n">
-        <f aca="false">D18</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="45" t="n">
-        <f aca="false">E18</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="45" t="n">
-        <f aca="false">F18</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="45" t="n">
-        <f aca="false">G18</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="45" t="n">
-        <f aca="false">H18</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="45" t="n">
-        <f aca="false">I18</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="45" t="n">
-        <f aca="false">J18</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="45" t="n">
-        <f aca="false">K18</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="45" t="n">
-        <f aca="false">L18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="s">
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+    </row>
+    <row r="22" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B22" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-    </row>
-    <row r="19" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="42" t="s">
         <v>189</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B23" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-    </row>
-    <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B24" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-    </row>
-    <row r="21" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B25" s="54" t="s">
         <v>194</v>
       </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-    </row>
-    <row r="22" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="46" t="s">
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="42" t="s">
         <v>195</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B26" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B27" s="40" t="s">
         <v>198</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="36" t="s">
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B28" s="40" t="s">
         <v>200</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="47" t="s">
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B29" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="s">
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B30" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="36" t="s">
-        <v>205</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>208</v>
-      </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/src/main/resources/reports/apk_9.xlsx
+++ b/src/main/resources/reports/apk_9.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="9.2.1" sheetId="1" state="visible" r:id="rId2"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="207">
   <si>
     <t xml:space="preserve">Наименование показателя</t>
   </si>
@@ -138,7 +138,10 @@
     <t xml:space="preserve">Площадь, га</t>
   </si>
   <si>
-    <t xml:space="preserve">Урожайность, кг</t>
+    <t xml:space="preserve">Урожайность, ц/га</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Валовый сбор, кг</t>
   </si>
   <si>
     <t xml:space="preserve">Затраты на производство (включая затраты незавершенного производства прошлых лет), относимые на себестоимость продукции отчетного года, тыс. руб</t>
@@ -185,9 +188,6 @@
   </si>
   <si>
     <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
   </si>
   <si>
     <t xml:space="preserve">ВСЕГО:
@@ -226,7 +226,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${winter_wheat.</t>
+      <t xml:space="preserve">${winter_wheat_harvest.</t>
     </r>
     <r>
       <rPr>
@@ -283,8 +283,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">${</t>
@@ -295,14 +295,15 @@
         <color rgb="FF6AAB73"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">crop_material_costs</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.winter_wheat.seeds}</t>
@@ -335,7 +336,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${spring_wheat.</t>
+      <t xml:space="preserve">${spring_wheat_harvest.</t>
     </r>
     <r>
       <rPr>
@@ -407,6 +408,7 @@
         <color rgb="FF6AAB73"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">crop_material_costs</t>
     </r>
@@ -468,6 +470,7 @@
         <color rgb="FF6AAB73"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">crop_material_costs</t>
     </r>
@@ -509,6 +512,7 @@
         <color rgb="FF6AAB73"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">crop_material_costs</t>
     </r>
@@ -591,7 +595,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${spring_barley.</t>
+      <t xml:space="preserve">${spring_barley_harvest.</t>
     </r>
     <r>
       <rPr>
@@ -663,6 +667,7 @@
         <color rgb="FF6AAB73"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">crop_material_costs</t>
     </r>
@@ -724,6 +729,7 @@
         <color rgb="FF6AAB73"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">crop_material_costs</t>
     </r>
@@ -765,6 +771,7 @@
         <color rgb="FF6AAB73"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">crop_material_costs</t>
     </r>
@@ -828,6 +835,9 @@
     <t xml:space="preserve">92200</t>
   </si>
   <si>
+    <t xml:space="preserve">Урожайность, кг</t>
+  </si>
+  <si>
     <t xml:space="preserve">Масличные культуры
 (стр.92310+ 92321+ 92322+ 92330+ 92390)</t>
   </si>
@@ -874,7 +884,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${sunflower.</t>
+      <t xml:space="preserve">${sunflower_harvest.</t>
     </r>
     <r>
       <rPr>
@@ -1136,6 +1146,9 @@
   </si>
   <si>
     <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
   </si>
   <si>
     <t xml:space="preserve">11</t>
@@ -1309,7 +1322,7 @@
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="[=0]\-;General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1379,16 +1392,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val=""/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF6AAB73"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1535,7 +1543,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1608,10 +1616,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1624,6 +1628,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1665,10 +1673,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1833,7 +1837,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55.12"/>
@@ -1859,104 +1863,115 @@
         <v>2</v>
       </c>
       <c r="D1" s="1"/>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="J3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="1"/>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="5" t="n">
         <v>8</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="38.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
@@ -1975,13 +1990,13 @@
         <f aca="false">E7+'9.2.2'!E6</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="10" t="e">
         <f aca="false">F7+'9.2.2'!F6</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <f aca="false">G7+'9.2.2'!G6</f>
         <v>0</v>
-      </c>
-      <c r="G6" s="10" t="e">
-        <f aca="false">G7+'9.2.2'!G6</f>
-        <v>#VALUE!</v>
       </c>
       <c r="H6" s="10" t="e">
         <f aca="false">H7+'9.2.2'!H6</f>
@@ -1995,8 +2010,12 @@
         <f aca="false">J7+'9.2.2'!J6</f>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="50.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K6" s="10" t="e">
+        <f aca="false">K7+'9.2.2'!K6</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
         <v>22</v>
       </c>
@@ -2015,13 +2034,13 @@
         <f aca="false">E8+E9+E16</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="13" t="e">
         <f aca="false">F8+F9+F16</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <f aca="false">G8+G9+G16</f>
         <v>0</v>
-      </c>
-      <c r="G7" s="13" t="e">
-        <f aca="false">G8+G9+G16</f>
-        <v>#VALUE!</v>
       </c>
       <c r="H7" s="13" t="e">
         <f aca="false">H8+H9+H16</f>
@@ -2035,8 +2054,12 @@
         <f aca="false">J8+J9+J16</f>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K7" s="13" t="e">
+        <f aca="false">K8+K9+K16</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
         <v>24</v>
       </c>
@@ -2049,27 +2072,31 @@
       <c r="D8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="e">
+        <f aca="false">F8/100/C8</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <f aca="false">SUM(G8:J8)</f>
+      <c r="G8" s="14" t="n">
+        <f aca="false">SUM(H8:K8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="H8" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="I8" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="J8" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="K8" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="80.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
         <v>33</v>
       </c>
@@ -2082,23 +2109,27 @@
       <c r="D9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="e">
+        <f aca="false">F9/100/C9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <f aca="false">SUM(G9:J9)</f>
+      <c r="G9" s="14" t="n">
+        <f aca="false">SUM(H9:K9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="H9" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="I9" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="J9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="K9" s="19" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2109,30 +2140,32 @@
       <c r="B10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-    </row>
-    <row r="11" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
@@ -2141,14 +2174,15 @@
       <c r="B12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
@@ -2157,14 +2191,15 @@
       <c r="B13" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
@@ -2173,14 +2208,15 @@
       <c r="B14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
@@ -2189,16 +2225,17 @@
       <c r="B15" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-    </row>
-    <row r="16" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="80.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
         <v>54</v>
       </c>
@@ -2211,41 +2248,46 @@
       <c r="D16" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="e">
+        <f aca="false">F16/100/C16</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F16" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="14" t="n">
-        <f aca="false">SUM(G16:J16)</f>
+      <c r="G16" s="14" t="n">
+        <f aca="false">SUM(H16:K16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="I16" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="J16" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="20" t="s">
+      <c r="K16" s="19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
         <v>63</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
@@ -2254,14 +2296,15 @@
       <c r="B18" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
@@ -2270,30 +2313,32 @@
       <c r="B19" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-    </row>
-    <row r="20" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
         <v>69</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
@@ -2302,14 +2347,15 @@
       <c r="B21" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
@@ -2320,26 +2366,28 @@
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="I22" s="25"/>
       <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:E4"/>
-    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="F1:F4"/>
+    <mergeCell ref="G1:K1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:K3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2357,7 +2405,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:ALZ32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="55.12"/>
@@ -2385,90 +2433,100 @@
         <v>2</v>
       </c>
       <c r="D1" s="3"/>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3"/>
+      <c r="F1" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="ALZ1" s="26"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="ALZ2" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="ALZ3" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="63.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="27"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="ALZ4" s="26"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="28" t="n">
         <v>6</v>
       </c>
       <c r="G5" s="6" t="n">
@@ -2483,13 +2541,17 @@
       <c r="J5" s="6" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K5" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="ALZ5" s="26"/>
+    </row>
+    <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="30" t="e">
         <f aca="false">C10+C7</f>
@@ -2500,16 +2562,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="E6" s="30" t="e">
-        <f aca="false">E10+E7</f>
+        <f aca="false">E10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="30" t="e">
         <f aca="false">F10+F7</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <f aca="false">G10+G7</f>
         <v>0</v>
-      </c>
-      <c r="G6" s="30" t="e">
-        <f aca="false">G10+G7</f>
-        <v>#VALUE!</v>
       </c>
       <c r="H6" s="30" t="e">
         <f aca="false">H10+H7</f>
@@ -2523,453 +2585,514 @@
         <f aca="false">J10+J7</f>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="41.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K6" s="30" t="e">
+        <f aca="false">K10+K7</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="ALZ6" s="26"/>
+    </row>
+    <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="32"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="ALZ7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
+        <v>81</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="ALZ8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-    </row>
-    <row r="10" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>83</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="ALZ9" s="26"/>
+    </row>
+    <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="C10" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="D10" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <f aca="false">SUM(G10:J10)</f>
+      <c r="E10" s="36" t="e">
+        <f aca="false">F10/100/C10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <f aca="false">SUM(H10:K10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="19" t="s">
         <v>91</v>
       </c>
+      <c r="K10" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="ALZ10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
+        <v>94</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="ALZ11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
+        <v>96</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="ALZ12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" s="40" t="s">
+      <c r="A13" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
+      <c r="B13" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="ALZ13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" s="40" t="s">
+      <c r="A14" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
+      <c r="B14" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="ALZ14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="A15" s="41" t="s">
         <v>101</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="ALZ15" s="26"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="40" t="s">
+      <c r="A16" s="41" t="s">
         <v>103</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>104</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="ALZ16" s="26"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="40" t="s">
+      <c r="A17" s="41" t="s">
         <v>105</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>106</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="ALZ17" s="26"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="40" t="s">
+      <c r="A18" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
+      <c r="B18" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="ALZ18" s="26"/>
     </row>
     <row r="19" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="40" t="s">
+      <c r="A19" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
+      <c r="B19" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="ALZ19" s="26"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="40" t="s">
+      <c r="A20" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
+      <c r="B20" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="ALZ20" s="26"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="40" t="s">
+      <c r="A21" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
+      <c r="B21" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="ALZ21" s="26"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="40" t="s">
+      <c r="A22" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
+      <c r="B22" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="ALZ22" s="26"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="40" t="s">
+      <c r="A23" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
+      <c r="B23" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="ALZ23" s="26"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="40" t="s">
+      <c r="A24" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
+      <c r="B24" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="ALZ24" s="26"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="40" t="s">
+      <c r="A25" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
+      <c r="B25" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="ALZ25" s="26"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="40" t="s">
+      <c r="A26" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
+      <c r="B26" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="ALZ26" s="26"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="B27" s="40" t="s">
+      <c r="A27" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
+      <c r="B27" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="ALZ27" s="26"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="40" t="s">
+      <c r="A28" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
+      <c r="B28" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="ALZ28" s="26"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="40" t="s">
+      <c r="A29" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
+      <c r="B29" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="ALZ29" s="26"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="B30" s="40" t="s">
+      <c r="A30" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
+      <c r="B30" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="40"/>
+      <c r="ALZ30" s="26"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="B31" s="40" t="s">
+      <c r="A31" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
+      <c r="B31" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="ALZ31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="44" t="s">
+      <c r="A32" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
+      <c r="B32" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="ALZ32" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:E4"/>
-    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="F1:F4"/>
+    <mergeCell ref="G1:K1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:K3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2999,11 +3122,11 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -3019,10 +3142,10 @@
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -3038,10 +3161,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -3053,7 +3176,7 @@
     </row>
     <row r="4" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
@@ -3061,607 +3184,607 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="L4" s="46" t="s">
         <v>147</v>
+      </c>
+      <c r="L4" s="45" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="49" t="n">
+      <c r="A6" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="48" t="n">
         <f aca="false">C13+C7+C25</f>
         <v>0</v>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="48" t="n">
         <f aca="false">D13+D7+D25</f>
         <v>0</v>
       </c>
-      <c r="E6" s="49" t="n">
+      <c r="E6" s="48" t="n">
         <f aca="false">E13+E7+E25</f>
         <v>0</v>
       </c>
-      <c r="F6" s="49" t="n">
+      <c r="F6" s="48" t="n">
         <f aca="false">F13+F7+F25</f>
         <v>0</v>
       </c>
-      <c r="G6" s="49" t="n">
+      <c r="G6" s="48" t="n">
         <f aca="false">G13+G7+G25</f>
         <v>0</v>
       </c>
-      <c r="H6" s="49" t="n">
+      <c r="H6" s="48" t="n">
         <f aca="false">H13+H7+H25</f>
         <v>0</v>
       </c>
-      <c r="I6" s="49" t="n">
+      <c r="I6" s="48" t="n">
         <f aca="false">I13+I7+I25</f>
         <v>0</v>
       </c>
-      <c r="J6" s="49" t="n">
+      <c r="J6" s="48" t="n">
         <f aca="false">J13+J7+J25</f>
         <v>0</v>
       </c>
-      <c r="K6" s="49" t="n">
+      <c r="K6" s="48" t="n">
         <f aca="false">K13+K7+K25</f>
         <v>0</v>
       </c>
-      <c r="L6" s="49" t="n">
+      <c r="L6" s="48" t="n">
         <f aca="false">L13+L7+L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
+      <c r="A7" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
+      <c r="A8" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
+      <c r="A9" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
+      <c r="A10" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+        <v>168</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+        <v>170</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="C13" s="50" t="n">
+      <c r="A13" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="49" t="n">
         <f aca="false">C17</f>
         <v>0</v>
       </c>
-      <c r="D13" s="50" t="n">
+      <c r="D13" s="49" t="n">
         <f aca="false">D17</f>
         <v>0</v>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="49" t="n">
         <f aca="false">E17</f>
         <v>0</v>
       </c>
-      <c r="F13" s="50" t="n">
+      <c r="F13" s="49" t="n">
         <f aca="false">F17</f>
         <v>0</v>
       </c>
-      <c r="G13" s="50" t="n">
+      <c r="G13" s="49" t="n">
         <f aca="false">G17</f>
         <v>0</v>
       </c>
-      <c r="H13" s="50" t="n">
+      <c r="H13" s="49" t="n">
         <f aca="false">H17</f>
         <v>0</v>
       </c>
-      <c r="I13" s="50" t="n">
+      <c r="I13" s="49" t="n">
         <f aca="false">I17</f>
         <v>0</v>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="49" t="n">
         <f aca="false">J17</f>
         <v>0</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="49" t="n">
         <f aca="false">K17</f>
         <v>0</v>
       </c>
-      <c r="L13" s="50" t="n">
+      <c r="L13" s="49" t="n">
         <f aca="false">L17</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
+      <c r="A14" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="B15" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
+      <c r="A15" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
+      <c r="A16" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
     </row>
     <row r="17" customFormat="false" ht="24.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="B17" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="51" t="n">
+      <c r="A17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="50" t="n">
         <f aca="false">C18</f>
         <v>0</v>
       </c>
-      <c r="D17" s="51" t="n">
+      <c r="D17" s="50" t="n">
         <f aca="false">D18</f>
         <v>0</v>
       </c>
-      <c r="E17" s="51" t="n">
+      <c r="E17" s="50" t="n">
         <f aca="false">E18</f>
         <v>0</v>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="50" t="n">
         <f aca="false">F18</f>
         <v>0</v>
       </c>
-      <c r="G17" s="51" t="n">
+      <c r="G17" s="50" t="n">
         <f aca="false">G18</f>
         <v>0</v>
       </c>
-      <c r="H17" s="51" t="n">
+      <c r="H17" s="50" t="n">
         <f aca="false">H18</f>
         <v>0</v>
       </c>
-      <c r="I17" s="51" t="n">
+      <c r="I17" s="50" t="n">
         <f aca="false">I18</f>
         <v>0</v>
       </c>
-      <c r="J17" s="51" t="n">
+      <c r="J17" s="50" t="n">
         <f aca="false">J18</f>
         <v>0</v>
       </c>
-      <c r="K17" s="51" t="n">
+      <c r="K17" s="50" t="n">
         <f aca="false">K18</f>
         <v>0</v>
       </c>
-      <c r="L17" s="51" t="n">
+      <c r="L17" s="50" t="n">
         <f aca="false">L18</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="52" t="s">
-        <v>179</v>
-      </c>
-      <c r="B18" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
+      <c r="A18" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="50"/>
+      <c r="L18" s="50"/>
     </row>
     <row r="19" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="42" t="s">
-        <v>181</v>
-      </c>
-      <c r="B19" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
+      <c r="A19" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
+      <c r="A20" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
     </row>
     <row r="21" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="42" t="s">
-        <v>185</v>
-      </c>
-      <c r="B21" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
+      <c r="A21" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="41"/>
+      <c r="A22" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="42" t="s">
-        <v>189</v>
-      </c>
-      <c r="B23" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
+      <c r="A23" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
+      <c r="A24" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="54" t="s">
-        <v>194</v>
-      </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
+      <c r="A25" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
+      <c r="A26" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B27" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
+      <c r="A27" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="42" t="s">
-        <v>199</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
+      <c r="A28" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="42" t="s">
-        <v>201</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
+      <c r="A29" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42" t="s">
-        <v>203</v>
-      </c>
-      <c r="B30" s="44" t="s">
-        <v>204</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
+      <c r="A30" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/src/main/resources/reports/apk_9.xlsx
+++ b/src/main/resources/reports/apk_9.xlsx
@@ -10,7 +10,6 @@
   <sheets>
     <sheet name="9.2.1" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="9.2.2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="9.4" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -48,7 +47,7 @@
             <family val="2"/>
             <charset val="204"/>
           </rPr>
-          <t xml:space="preserve">jx:area(lastCell="J22")</t>
+          <t xml:space="preserve">jx:area(lastCell="K22")</t>
         </r>
       </text>
     </comment>
@@ -91,43 +90,8 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author> </author>
-  </authors>
-  <commentList>
-    <comment ref="C6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Автор:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">jx:area(lastCell="P31")</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="138">
   <si>
     <t xml:space="preserve">Наименование показателя</t>
   </si>
@@ -144,7 +108,7 @@
     <t xml:space="preserve">Валовый сбор, кг</t>
   </si>
   <si>
-    <t xml:space="preserve">Затраты на производство (включая затраты незавершенного производства прошлых лет), относимые на себестоимость продукции отчетного года, тыс. руб</t>
+    <t xml:space="preserve">Затраты на производство (включая затраты незавершенного производства прошлых лет), относимые на себестоимость продукции отчетного года, руб</t>
   </si>
   <si>
     <t xml:space="preserve">Наименование культуры/ вида продукции</t>
@@ -310,10 +274,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">${crop_material_costs.winter_wheat.fertilizersUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${crop_material_costs.winter_wheat.fuelUsed}</t>
+    <t xml:space="preserve">${crop_material_costs.winter_wheat.fertilizer}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${crop_material_costs.winter_wheat.fuel}</t>
   </si>
   <si>
     <t xml:space="preserve">пшеница яровая</t>
@@ -492,7 +456,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">spring_wheat.fertilizersUsed}</t>
+      <t xml:space="preserve">spring_wheat.fertilizer}</t>
     </r>
   </si>
   <si>
@@ -534,7 +498,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">spring_wheat.fuelUsed}</t>
+      <t xml:space="preserve">spring_wheat.fuel}</t>
     </r>
   </si>
   <si>
@@ -751,7 +715,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">spring_barley.fertilizersUsed}</t>
+      <t xml:space="preserve">spring_barley.fertilizer}</t>
     </r>
   </si>
   <si>
@@ -793,7 +757,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">spring_barley.fuelUsed}</t>
+      <t xml:space="preserve">spring_barley.fuel}</t>
     </r>
   </si>
   <si>
@@ -836,6 +800,9 @@
   </si>
   <si>
     <t xml:space="preserve">Урожайность, кг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Затраты на производство (включая затраты незавершенного производства прошлых лет), относимые на себестоимость продукции отчетного года, тыс. руб</t>
   </si>
   <si>
     <t xml:space="preserve">Масличные культуры
@@ -943,10 +910,10 @@
     <t xml:space="preserve">${crop_material_costs.sunflower.seeds}</t>
   </si>
   <si>
-    <t xml:space="preserve">${crop_material_costs.sunflower.fertilizersUsed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${crop_material_costs.sunflower.fuelUsed}</t>
+    <t xml:space="preserve">${crop_material_costs.sunflower.fertilizer}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${crop_material_costs.sunflower.fuel}</t>
   </si>
   <si>
     <t xml:space="preserve">из него 
@@ -1085,232 +1052,6 @@
   </si>
   <si>
     <t xml:space="preserve">92490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Показатель</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Затраты на многолетние насаждения, вступившие в период товарного плодоношения, тыс. руб</t>
-  </si>
-  <si>
-    <t xml:space="preserve">всего 
-(гр.4+ 5+ 6+ 7+ 8+ 9+ 10+ 11+ 12+ 13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оплата труда 
-с отчислениями на социальные нужды</t>
-  </si>
-  <si>
-    <t xml:space="preserve">минеральные удобрения, бактериальные и другие препараты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">средства защиты растений</t>
-  </si>
-  <si>
-    <t xml:space="preserve">покупная энергия всех видов, топливо, кроме нефте-
-продуктов (уголь, газ, дрова)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в т.ч. газ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">электро- энергия</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нефте-
-продукты всех видов, использу-
-емые на технологи-
-ческие цели</t>
-  </si>
-  <si>
-    <t xml:space="preserve">содержание основных средств (запасные части 
-и расходные материалы, текущий ремонт)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оплата работ и услуг производственного характера, в т.ч. выполненных сторонними организациями, прочие материальные затраты (предметы труда, используемые в производстве)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ВСЕГО:
-(стр.94100+ 94200+ 94300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Культуры, для производства напитков, пряности и растения, используемые в парфюмерии и фармации (стр.94110+ 94120+ 94190)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в том числе: 
-плантации чая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">хмельники</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">прочие культуры, не включенные в другие 
-группировки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в том числе: 
-лекарственные культуры</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">эфиромасличные культуры травянистые однолетние и двулетние</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Плодовые и ягодные многолетние насаждения, включая виноградники (стр.94210+ 94220+ 94230+ 94240+ 94250+ 94260+ 94270+ 94280+ 94290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в том числе:
-виноградники</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">тропические и субтропические культуры 
-(авокадо, бананы, финики, инжир)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">цитрусовые культуры (грейпфруты, лимоны и лаймы, апельсины, мандарины, включая танжерины, клементины и аналогичные гибриды цитрусовых культур)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">семечковые культуры (яблоня, груша, айва)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">из них: 
-яблони</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">косточковые культуры 
-(абрикос, вишня, персики, нектарины, сливы, терн)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">прочие семечковые и косточковые культуры, не включенные в другие группировки (черешня, алыча (ткемали, вишнеслива), барбарис, кизил)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">кустарниковые ягодные растения (киви, малина, замляника, клюква, черника всех видов, брусника, голубика, смородина, крыжовник)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">из них:
-земляника (клубника)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">орехоплодовые культуры (миндаль, каштаны, фундук, фисташки, орехи грецкие, прочие)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">прочие плодовые и ягодные многолетние насаждения, не включенные в другие группировки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Питомники плодовых и ягодных насаждений (стр.94301+ 94302+ 94303+ 94304+ 94305)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">саженцы семечковых культур</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">саженцы косточковых культур</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">саженцы ягодных кустарниковых культур</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">саженцы винограда</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">прочая продукция питомников</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94305</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1154,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1426,20 +1167,8 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E0B4"/>
-        <bgColor rgb="FFAFD095"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FFC5E0B4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1503,20 +1232,6 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1543,7 +1258,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1584,7 +1299,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1596,31 +1311,87 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1628,74 +1399,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1722,42 +1425,6 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1785,7 +1452,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -1805,7 +1472,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC5E0B4"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1849,6 +1516,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1014" style="0" width="9.14"/>
   </cols>
   <sheetData>
@@ -2096,7 +1764,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="80.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="56.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
         <v>33</v>
       </c>
@@ -2140,32 +1808,32 @@
       <c r="B10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
@@ -2174,15 +1842,15 @@
       <c r="B12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
@@ -2191,15 +1859,15 @@
       <c r="B13" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
@@ -2208,15 +1876,15 @@
       <c r="B14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
@@ -2225,17 +1893,17 @@
       <c r="B15" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" customFormat="false" ht="80.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="56.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
         <v>54</v>
       </c>
@@ -2273,21 +1941,21 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>63</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
@@ -2296,15 +1964,15 @@
       <c r="B18" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
@@ -2313,32 +1981,32 @@
       <c r="B19" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="21" t="s">
         <v>69</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
@@ -2347,32 +2015,32 @@
       <c r="B21" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2408,17 +2076,17 @@
   <dimension ref="A1:ALZ32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="55.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="9.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="15.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="26" width="17.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="26" width="19.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="26" width="15.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="26" width="17.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="26" width="12.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="26" width="15.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="26" width="14.4"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1013" min="11" style="26" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="25" width="55.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="9.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="15.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="25" width="17.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="19.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="25" width="15.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="25" width="17.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="25" width="12.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="25" width="15.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="25" width="14.4"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1013" min="11" style="25" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1014" style="0" width="9.14"/>
   </cols>
   <sheetData>
@@ -2436,17 +2104,17 @@
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>75</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
-      <c r="ALZ1" s="26"/>
+      <c r="ALZ1" s="25"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -2460,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="27"/>
+      <c r="F2" s="26"/>
       <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
@@ -2470,7 +2138,7 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="ALZ2" s="26"/>
+      <c r="ALZ2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
@@ -2478,7 +2146,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="27"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
         <v>11</v>
@@ -2488,7 +2156,7 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="ALZ3" s="26"/>
+      <c r="ALZ3" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="63.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
@@ -2496,7 +2164,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="27"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
@@ -2508,7 +2176,7 @@
       <c r="K4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="ALZ4" s="26"/>
+      <c r="ALZ4" s="25"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
@@ -2526,7 +2194,7 @@
       <c r="E5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="27" t="n">
         <v>6</v>
       </c>
       <c r="G5" s="6" t="n">
@@ -2544,540 +2212,540 @@
       <c r="K5" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="ALZ5" s="26"/>
+      <c r="ALZ5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="30" t="e">
+      <c r="B6" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="29" t="e">
         <f aca="false">C10+C7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D6" s="30" t="e">
+      <c r="D6" s="29" t="e">
         <f aca="false">D10+D7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E6" s="30" t="e">
+      <c r="E6" s="29" t="e">
         <f aca="false">E10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F6" s="30" t="e">
+      <c r="F6" s="29" t="e">
         <f aca="false">F10+F7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="29" t="n">
         <f aca="false">G10+G7</f>
         <v>0</v>
       </c>
-      <c r="H6" s="30" t="e">
+      <c r="H6" s="29" t="e">
         <f aca="false">H10+H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I6" s="30" t="e">
+      <c r="I6" s="29" t="e">
         <f aca="false">I10+I7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J6" s="30" t="e">
+      <c r="J6" s="29" t="e">
         <f aca="false">J10+J7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K6" s="30" t="e">
+      <c r="K6" s="29" t="e">
         <f aca="false">K10+K7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="ALZ6" s="26"/>
+      <c r="ALZ6" s="25"/>
     </row>
     <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="ALZ7" s="26"/>
+      <c r="B7" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="ALZ7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="ALZ8" s="26"/>
+      <c r="B8" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="ALZ8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="ALZ9" s="26"/>
+      <c r="B9" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="ALZ9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="B10" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="C10" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="36" t="e">
+      <c r="D10" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="33" t="e">
         <f aca="false">F10/100/C10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F10" s="37" t="s">
-        <v>88</v>
+      <c r="F10" s="31" t="s">
+        <v>89</v>
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">SUM(H10:K10)</f>
         <v>0</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="ALZ10" s="26"/>
+        <v>93</v>
+      </c>
+      <c r="ALZ10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="31" t="s">
+      <c r="A11" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="ALZ11" s="26"/>
+      <c r="B11" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="ALZ11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="ALZ12" s="26"/>
+      <c r="B12" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="ALZ12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" s="39" t="s">
+      <c r="A13" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="ALZ13" s="26"/>
+      <c r="B13" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="ALZ13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="39" t="s">
+      <c r="A14" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="ALZ14" s="26"/>
+      <c r="B14" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="ALZ14" s="25"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="39" t="s">
+      <c r="A15" s="38" t="s">
         <v>102</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="ALZ15" s="26"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="ALZ15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="39" t="s">
+      <c r="A16" s="38" t="s">
         <v>104</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>105</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="ALZ16" s="26"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="ALZ16" s="25"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="39" t="s">
+      <c r="A17" s="38" t="s">
         <v>106</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="ALZ17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="ALZ17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="39" t="s">
+      <c r="A18" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="ALZ18" s="26"/>
+      <c r="B18" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="ALZ18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="39" t="s">
+      <c r="A19" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="ALZ19" s="26"/>
+      <c r="B19" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="ALZ19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="39" t="s">
+      <c r="A20" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="ALZ20" s="26"/>
+      <c r="B20" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="ALZ20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="39" t="s">
+      <c r="A21" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="ALZ21" s="26"/>
+      <c r="B21" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="ALZ21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="39" t="s">
+      <c r="A22" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="ALZ22" s="26"/>
+      <c r="B22" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="ALZ22" s="25"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" s="39" t="s">
+      <c r="A23" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="ALZ23" s="26"/>
+      <c r="B23" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="ALZ23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="B24" s="39" t="s">
+      <c r="A24" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="ALZ24" s="26"/>
+      <c r="B24" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="ALZ24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="39" t="s">
+      <c r="A25" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="ALZ25" s="26"/>
+      <c r="B25" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="ALZ25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="B26" s="39" t="s">
+      <c r="A26" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="ALZ26" s="26"/>
+      <c r="B26" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="ALZ26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="B27" s="39" t="s">
+      <c r="A27" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="ALZ27" s="26"/>
+      <c r="B27" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="ALZ27" s="25"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="B28" s="39" t="s">
+      <c r="A28" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="ALZ28" s="26"/>
+      <c r="B28" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="ALZ28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="B29" s="39" t="s">
+      <c r="A29" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="ALZ29" s="26"/>
+      <c r="B29" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="ALZ29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" s="39" t="s">
+      <c r="A30" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="ALZ30" s="26"/>
+      <c r="B30" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="ALZ30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="B31" s="39" t="s">
+      <c r="A31" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
-      <c r="ALZ31" s="26"/>
+      <c r="B31" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="ALZ31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="B32" s="43" t="s">
+      <c r="A32" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="ALZ32" s="26"/>
+      <c r="B32" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="ALZ32" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3103,705 +2771,4 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="71.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="3" style="0" width="13.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1021" style="0" width="9.14"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="L4" s="45" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="48" t="n">
-        <f aca="false">C13+C7+C25</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="48" t="n">
-        <f aca="false">D13+D7+D25</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="48" t="n">
-        <f aca="false">E13+E7+E25</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="48" t="n">
-        <f aca="false">F13+F7+F25</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="48" t="n">
-        <f aca="false">G13+G7+G25</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="48" t="n">
-        <f aca="false">H13+H7+H25</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="48" t="n">
-        <f aca="false">I13+I7+I25</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="48" t="n">
-        <f aca="false">J13+J7+J25</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="48" t="n">
-        <f aca="false">K13+K7+K25</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="48" t="n">
-        <f aca="false">L13+L7+L25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-    </row>
-    <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-    </row>
-    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-    </row>
-    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-    </row>
-    <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="49" t="n">
-        <f aca="false">C17</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="49" t="n">
-        <f aca="false">D17</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="49" t="n">
-        <f aca="false">E17</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="49" t="n">
-        <f aca="false">F17</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="49" t="n">
-        <f aca="false">G17</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="49" t="n">
-        <f aca="false">H17</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="49" t="n">
-        <f aca="false">I17</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="49" t="n">
-        <f aca="false">J17</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="49" t="n">
-        <f aca="false">K17</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="49" t="n">
-        <f aca="false">L17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-    </row>
-    <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-    </row>
-    <row r="16" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-    </row>
-    <row r="17" customFormat="false" ht="24.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <f aca="false">C18</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <f aca="false">D18</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="50" t="n">
-        <f aca="false">E18</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="50" t="n">
-        <f aca="false">F18</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="50" t="n">
-        <f aca="false">G18</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="50" t="n">
-        <f aca="false">H18</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="50" t="n">
-        <f aca="false">I18</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="50" t="n">
-        <f aca="false">J18</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="50" t="n">
-        <f aca="false">K18</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="50" t="n">
-        <f aca="false">L18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
-    </row>
-    <row r="19" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-    </row>
-    <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-    </row>
-    <row r="21" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>188</v>
-      </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-    </row>
-    <row r="22" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="B25" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="B30" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:L2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:L3"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>